--- a/xll_example/xlTest.xlsx
+++ b/xll_example/xlTest.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\root\dev\savine_scripting_cmake\xll_example\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\root\dev\savine_scripting\xll_example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5917012-7DC3-4332-B6FF-8855E288B54C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B24CB3-1DF2-42D8-BA53-E7BC0C8756A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1611,7 +1611,7 @@
         <v>21</v>
       </c>
       <c r="B9" s="15">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K9" s="20" t="s">
         <v>27</v>
@@ -2034,12 +2034,11 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30" s="17" t="str">
-        <f t="array" aca="1" ref="A30:B33" ca="1">_xll.TestScript(B2,B3,B4,B5,A12:A27,B12:B27,B9,B8)</f>
+        <f t="array" ref="A30:B33">_xll.TestScript(B2,B3,B4,B5,A12:A27,B12:B27,B9,B8)</f>
         <v>ALIVE</v>
       </c>
       <c r="B30" s="18">
-        <f ca="1"/>
-        <v>0.6</v>
+        <v>0.43000000000000022</v>
       </c>
       <c r="K30" s="19" t="s">
         <v>37</v>
@@ -2047,12 +2046,10 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31" s="17" t="str">
-        <f ca="1"/>
         <v>AUTOCALL</v>
       </c>
       <c r="B31" s="18">
-        <f ca="1"/>
-        <v>84</v>
+        <v>89.1</v>
       </c>
       <c r="K31" s="13">
         <v>42104</v>
@@ -2070,11 +2067,9 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32" s="17" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="B32" s="18" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="K32" s="13">
@@ -2093,11 +2088,9 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33" s="17" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="B33" s="18" t="e">
-        <f ca="1"/>
         <v>#N/A</v>
       </c>
       <c r="K33" s="13">
